--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/sep-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/sep-2026.xlsx
@@ -1172,7 +1172,11 @@
           <t>79.744.580-0</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1416,7 +1420,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1538,7 +1546,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1660,7 +1672,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1782,7 +1798,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1965,7 +1985,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2087,7 +2111,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2148,7 +2176,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2209,7 +2241,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2453,7 +2489,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2697,7 +2737,11 @@
           <t>78.874.470-6</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2758,7 +2802,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2819,7 +2867,11 @@
           <t>77.535.386-4</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3124,7 +3176,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4039,7 +4095,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4405,7 +4465,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4527,7 +4591,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4588,7 +4656,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
@@ -4893,7 +4965,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5686,7 +5762,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
@@ -5869,7 +5949,11 @@
           <t>76.556.146-9</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6052,7 +6136,11 @@
           <t>92.288.000-k</t>
         </is>
       </c>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6113,7 +6201,11 @@
           <t>77.447.444-7</t>
         </is>
       </c>
-      <c r="K93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6174,7 +6266,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L94" t="inlineStr">
         <is>
           <t>USD</t>
@@ -6479,7 +6575,11 @@
           <t>78.233.420-4</t>
         </is>
       </c>
-      <c r="K99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L99" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/sep-2026.xlsx
+++ b/docs/oc-mensuales/endoprotesis-ortopedia-y-trauma/sep-2026.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M103"/>
+  <dimension ref="A1:M115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -745,7 +745,11 @@
           <t>93.745.000-1</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1083,7 +1087,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1124,7 +1128,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1622-1131-CM26</t>
+          <t>2107-1811-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1144,17 +1148,17 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.602.141-9</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,32 +1168,28 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>BLUNDING S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>79.744.580-0</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>2476.89</v>
+        <v>2413.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1057539-7216-CM26</t>
+          <t>1622-1131-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,53 +1204,57 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.141-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SAN VICENTE DE TAGUA TAGUA</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BLUNDING S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+          <t>79.744.580-0</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>76374.17999999999</v>
+        <v>2476.89</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1057539-7181-CM26</t>
+          <t>1057539-7216-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1290,12 +1294,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1305,13 +1309,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>12315.46</v>
+        <v>76374.17999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1063538-6400-CM26</t>
+          <t>1057539-7181-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1331,17 +1335,17 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.602.260-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>HOSPITAL BASE OSORNO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1351,12 +1355,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1366,13 +1370,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>2567.28</v>
+        <v>12315.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2111-9761-CM26</t>
+          <t>1063538-6400-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1392,46 +1396,46 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.602.260-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>HOSPITAL BASE OSORNO</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>6386.44</v>
+        <v>2567.28</v>
       </c>
     </row>
     <row r="17">
@@ -1498,7 +1502,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2111-11996-CM26</t>
+          <t>2111-9761-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1538,12 +1542,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>78.874.470-6</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1557,13 +1561,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>3832.02</v>
+        <v>6386.44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>1002772-9216-CM26</t>
+          <t>2111-11996-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1578,7 +1582,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1588,12 +1592,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.608.205-1</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1603,28 +1607,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>4104.9</v>
+        <v>3832.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>1057539-7288-CM26</t>
+          <t>1002772-9216-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1649,27 +1657,27 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.205-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO SALUD OCCIDENTE HOSPITAL DR FELIX BULNES CERDA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -1683,13 +1691,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>7601.14</v>
+        <v>4104.9</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>1057539-7289-CM26</t>
+          <t>1057539-7287-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1729,12 +1737,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1744,13 +1752,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>74730.62</v>
+        <v>54179.57</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1057439-5807-CM26</t>
+          <t>1057539-7288-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1770,32 +1778,32 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.606.402-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -1809,13 +1817,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>11422.96</v>
+        <v>7601.14</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>5326-1217-CM26</t>
+          <t>1057539-7289-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1840,27 +1848,27 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.602.140-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>GLOBALMED SpA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>76.400.383-7</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1870,13 +1878,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>38166.18</v>
+        <v>74730.62</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1422824-2915-CM26</t>
+          <t>1057539-7290-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1891,7 +1899,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1901,27 +1909,27 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1931,13 +1939,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>4416.89</v>
+        <v>66609</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057539-7408-CM26</t>
+          <t>1057439-5807-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1952,37 +1960,37 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.402-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL LA SERENA</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
+          <t>78.233.420-4</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -1996,13 +2004,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>5088.08</v>
+        <v>11422.96</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057539-7405-CM26</t>
+          <t>5326-1217-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2017,7 +2025,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2027,27 +2035,27 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.140-0</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE RENGO</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2057,13 +2065,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>72780.28</v>
+        <v>38166.18</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>699866-8944-CM26</t>
+          <t>1422824-2915-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2088,47 +2096,43 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4075.56</v>
+        <v>4416.89</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>538598-3123-CM26</t>
+          <t>1057539-7408-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2148,52 +2152,52 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.979.450-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>4330.28</v>
+        <v>5088.08</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1549-3809-CM26</t>
+          <t>1057539-7405-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2208,57 +2212,53 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>2599.64</v>
+        <v>72780.28</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>3328-2294-CM26</t>
+          <t>699866-8944-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2273,53 +2273,57 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>ARENYS MED S.A.</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>76.901.400-4</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>4460.17</v>
+        <v>4075.56</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1422830-169-CM26</t>
+          <t>538598-3123-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2334,53 +2338,57 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.979.450-8</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>HOSPITAL METROPOLITANO DE SANTIAGO</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>6255.76</v>
+        <v>4330.28</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1380-11059-CM26</t>
+          <t>1549-3809-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2405,43 +2413,47 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>2320.18</v>
+        <v>2599.64</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>1057501-10358-CM26</t>
+          <t>3328-2294-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2461,17 +2473,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -2481,32 +2493,28 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>ARENYS MED S.A.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.901.400-4</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>6626.54</v>
+        <v>4460.17</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>617807-4871-CM26</t>
+          <t>1422830-169-CM26</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2521,22 +2529,22 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>61.602.036-6</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2546,12 +2554,12 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K34" t="inlineStr"/>
@@ -2561,13 +2569,13 @@
         </is>
       </c>
       <c r="M34" s="2" t="n">
-        <v>7653.58</v>
+        <v>6255.76</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2258-7186-CM26</t>
+          <t>1380-11059-CM26</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2582,7 +2590,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2592,27 +2600,27 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K35" t="inlineStr"/>
@@ -2622,13 +2630,13 @@
         </is>
       </c>
       <c r="M35" s="2" t="n">
-        <v>22225.28</v>
+        <v>2320.18</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>1057543-1517-CM26</t>
+          <t>1057501-10358-CM26</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2643,7 +2651,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -2653,43 +2661,47 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>61.607.201-3</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M36" s="2" t="n">
-        <v>2671.32</v>
+        <v>6626.54</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>4502-812-CM26</t>
+          <t>617807-4871-CM26</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2709,52 +2721,48 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.602.036-6</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>SERV NAC SALUD HOSPITAL DE LOS ANDES</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>78.874.470-6</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M37" s="2" t="n">
-        <v>2365.39</v>
+        <v>7653.58</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>1979-4226-CM26</t>
+          <t>2258-7186-CM26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2769,7 +2777,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -2779,47 +2787,43 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>61.607.401-6</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ARAUCANIA SUR HOSPITAL DE NUEVA IMPERIAL</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M38" s="2" t="n">
-        <v>2363.06</v>
+        <v>22225.28</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>608-10990-CM26</t>
+          <t>1057543-1517-CM26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2834,57 +2838,53 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.607.201-3</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>AETICA SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>77.535.386-4</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M39" s="2" t="n">
-        <v>2942.39</v>
+        <v>2671.32</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>1057539-7406-CM26</t>
+          <t>4502-812-CM26</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2899,7 +2899,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -2909,43 +2909,47 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>STRYKER CORPORATION CHILE Y COMPANIA LIMITADA</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
+          <t>78.874.470-6</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M40" s="2" t="n">
-        <v>67456.19</v>
+        <v>2365.39</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>1057539-7407-CM26</t>
+          <t>2111-12333-CM26</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -2960,7 +2964,7 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -2970,27 +2974,27 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K41" t="inlineStr"/>
@@ -3000,13 +3004,13 @@
         </is>
       </c>
       <c r="M41" s="2" t="n">
-        <v>55324.51</v>
+        <v>10923.68</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>1057539-7572-CM26</t>
+          <t>2107-1901-CM26</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3021,7 +3025,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -3031,27 +3035,27 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.602.148-6</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD HOSPITAL DE SANTA CRUZ</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K42" t="inlineStr"/>
@@ -3061,13 +3065,13 @@
         </is>
       </c>
       <c r="M42" s="2" t="n">
-        <v>7299.34</v>
+        <v>7710.83</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>1549-4039-CM26</t>
+          <t>1057543-1528-CM26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3082,7 +3086,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -3092,27 +3096,27 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.607.201-3</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD TALCAHUANO HOSPITAL DE</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>GLOBALMED SpA</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.400.383-7</t>
         </is>
       </c>
       <c r="K43" t="inlineStr"/>
@@ -3122,13 +3126,13 @@
         </is>
       </c>
       <c r="M43" s="2" t="n">
-        <v>7237.75</v>
+        <v>9074.370000000001</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>1057539-7603-CM26</t>
+          <t>1979-4226-CM26</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3143,27 +3147,27 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.607.401-6</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ARAUCANIA SUR HOSPITAL DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3187,13 +3191,13 @@
         </is>
       </c>
       <c r="M44" s="2" t="n">
-        <v>5041.03</v>
+        <v>2363.06</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>1057539-7619-CM26</t>
+          <t>608-10990-CM26</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3208,53 +3212,57 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>AETICA SPA</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+          <t>77.535.386-4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M45" s="2" t="n">
-        <v>72993.36</v>
+        <v>2942.39</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>1057049-18220-CM26</t>
+          <t>1057539-7406-CM26</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3274,32 +3282,32 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K46" t="inlineStr"/>
@@ -3309,13 +3317,13 @@
         </is>
       </c>
       <c r="M46" s="2" t="n">
-        <v>74059.52</v>
+        <v>67456.19</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>812030-917-CM26</t>
+          <t>1057539-7407-CM26</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3330,7 +3338,7 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -3340,27 +3348,27 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K47" t="inlineStr"/>
@@ -3370,13 +3378,13 @@
         </is>
       </c>
       <c r="M47" s="2" t="n">
-        <v>10301.25</v>
+        <v>55324.51</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>1380-11351-CM26</t>
+          <t>1057539-7572-CM26</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3391,7 +3399,7 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -3401,27 +3409,27 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>61.602.232-6</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
@@ -3431,13 +3439,13 @@
         </is>
       </c>
       <c r="M48" s="2" t="n">
-        <v>2302.7</v>
+        <v>7299.34</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>1057539-7692-CM26</t>
+          <t>1549-4039-CM26</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3452,7 +3460,7 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -3462,27 +3470,27 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>OSTEOTRAUMA SPA</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>76.965.562-K</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K49" t="inlineStr"/>
@@ -3492,13 +3500,13 @@
         </is>
       </c>
       <c r="M49" s="2" t="n">
-        <v>16694.48</v>
+        <v>7237.75</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>3378-7927-CM26</t>
+          <t>1057539-7603-CM26</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3513,7 +3521,7 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -3523,43 +3531,47 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>61.101.030-3</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
       <c r="L50" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M50" s="2" t="n">
-        <v>2753.86</v>
+        <v>5041.03</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>5083-469-CM26</t>
+          <t>1057539-7619-CM26</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3574,37 +3586,37 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Medyssey</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>76.485.678-3</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K51" t="inlineStr"/>
@@ -3614,13 +3626,13 @@
         </is>
       </c>
       <c r="M51" s="2" t="n">
-        <v>18675.72</v>
+        <v>72993.36</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2080-9036-CM26</t>
+          <t>1057049-18220-CM26</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3635,37 +3647,37 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>PRODUCTOS MEDICOS LIMITADA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>78.073.910-k</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3675,13 +3687,13 @@
         </is>
       </c>
       <c r="M52" s="2" t="n">
-        <v>24443.23</v>
+        <v>74059.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2258-7398-CM26</t>
+          <t>812030-917-CM26</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3696,7 +3708,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -3706,43 +3718,47 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>61.606.201-8</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M53" s="2" t="n">
-        <v>18783.26</v>
+        <v>10301.25</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>5083-471-CM26</t>
+          <t>1380-11351-CM26</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -3757,7 +3773,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -3767,27 +3783,27 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>61.606.903-9</t>
+          <t>61.602.232-6</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
+          <t>HOSPITAL DOCTOR HERNAN HENRIQUEZ ARAVENA</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K54" t="inlineStr"/>
@@ -3797,13 +3813,13 @@
         </is>
       </c>
       <c r="M54" s="2" t="n">
-        <v>4026.45</v>
+        <v>2302.7</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>1057491-5321-CM26</t>
+          <t>1057539-7692-CM26</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -3818,37 +3834,37 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>NEUMANN LIMITADA</t>
+          <t>OSTEOTRAUMA SPA</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>78.936.310-2</t>
+          <t>76.965.562-K</t>
         </is>
       </c>
       <c r="K55" t="inlineStr"/>
@@ -3858,13 +3874,13 @@
         </is>
       </c>
       <c r="M55" s="2" t="n">
-        <v>5825.25</v>
+        <v>16694.48</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>1549-4107-CM26</t>
+          <t>3378-7927-CM26</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -3879,7 +3895,7 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -3889,12 +3905,12 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.101.030-3</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3904,12 +3920,12 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K56" t="inlineStr"/>
@@ -3919,13 +3935,13 @@
         </is>
       </c>
       <c r="M56" s="2" t="n">
-        <v>73125.41</v>
+        <v>2753.86</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>1057049-17695-CM26</t>
+          <t>5083-469-CM26</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -3940,37 +3956,37 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>Medyssey</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>76.485.678-3</t>
         </is>
       </c>
       <c r="K57" t="inlineStr"/>
@@ -3980,13 +3996,13 @@
         </is>
       </c>
       <c r="M57" s="2" t="n">
-        <v>6345.23</v>
+        <v>18675.72</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>1171142-3234-CM26</t>
+          <t>2080-9036-CM26</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4001,37 +4017,37 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>62.000.830-3</t>
+          <t>61.602.138-9</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>PRODUCTOS MEDICOS LIMITADA</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>78.073.910-k</t>
         </is>
       </c>
       <c r="K58" t="inlineStr"/>
@@ -4041,13 +4057,13 @@
         </is>
       </c>
       <c r="M58" s="2" t="n">
-        <v>6013.97</v>
+        <v>24443.23</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>1057402-9564-CM26</t>
+          <t>2258-7398-CM26</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4062,7 +4078,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -4072,47 +4088,43 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.606.201-8</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>SERVICIO DE SALUD ANTOFAGASTA HOSPITAL L</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M59" s="2" t="n">
-        <v>5336.51</v>
+        <v>18783.26</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>1057501-10748-CM26</t>
+          <t>5083-471-CM26</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4127,7 +4139,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -4137,17 +4149,17 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>61.606.903-9</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CURICO</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4167,13 +4179,13 @@
         </is>
       </c>
       <c r="M60" s="2" t="n">
-        <v>38997.52</v>
+        <v>4026.45</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>1549-4099-CM26</t>
+          <t>1057491-5321-CM26</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4188,22 +4200,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -4213,12 +4225,12 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K61" t="inlineStr"/>
@@ -4228,13 +4240,13 @@
         </is>
       </c>
       <c r="M61" s="2" t="n">
-        <v>10310.62</v>
+        <v>5825.25</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>1422830-176-CM26</t>
+          <t>1057049-17695-CM26</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4259,27 +4271,27 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>61.602.054-4</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K62" t="inlineStr"/>
@@ -4289,13 +4301,13 @@
         </is>
       </c>
       <c r="M62" s="2" t="n">
-        <v>68109.3</v>
+        <v>6345.23</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>1057501-10834-CM26</t>
+          <t>1171142-3234-CM26</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4310,7 +4322,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -4320,43 +4332,47 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>61.608.502-6</t>
+          <t>62.000.830-3</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
+          <t>HOSPITAL COMPLEJO ASISTENCIAL PADRE LAS CASAS</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
+          <t>Araucanía</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>78.566.250-4</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M63" s="2" t="n">
-        <v>15194.46</v>
+        <v>6013.97</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>1057417-15577-CM26</t>
+          <t>1057402-9564-CM26</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4371,7 +4387,7 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -4381,43 +4397,47 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.607.301-K</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L64" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M64" s="2" t="n">
-        <v>34172.86</v>
+        <v>5336.51</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>4502-683-CM26</t>
+          <t>1057501-10748-CM26</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4432,57 +4452,53 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M65" s="2" t="n">
-        <v>11549.37</v>
+        <v>38997.52</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2111-12184-CM26</t>
+          <t>1549-4099-CM26</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4497,7 +4513,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -4507,12 +4523,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -4522,12 +4538,12 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K66" t="inlineStr"/>
@@ -4537,13 +4553,13 @@
         </is>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3422.72</v>
+        <v>10310.62</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2111-12249-CM26</t>
+          <t>1549-4107-CM26</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4558,22 +4574,22 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -4583,32 +4599,28 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr"/>
       <c r="L67" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M67" s="2" t="n">
-        <v>2472.17</v>
+        <v>73125.41</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2111-12471-CM26</t>
+          <t>1422830-176-CM26</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -4623,57 +4635,53 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.602.054-4</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL CARLOS VAN BUREN</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M68" s="2" t="n">
-        <v>3336.48</v>
+        <v>68109.3</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2111-12494-CM26</t>
+          <t>1057417-15578-CM26</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -4688,37 +4696,37 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>61.608.602-2</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K69" t="inlineStr"/>
@@ -4728,13 +4736,13 @@
         </is>
       </c>
       <c r="M69" s="2" t="n">
-        <v>2908.73</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>4817-3433-CM26</t>
+          <t>1057501-10834-CM26</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -4749,7 +4757,7 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -4759,27 +4767,27 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>61.606.917-9</t>
+          <t>61.608.502-6</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
+          <t>COMPLEJO ASISTENCIAL DR. SOTERO DEL RIO</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>TECNIKA S A</t>
+          <t>PRODUCTOS MEDICOS PROMEDON CHILE S A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>96.625.950-7</t>
+          <t>78.566.250-4</t>
         </is>
       </c>
       <c r="K70" t="inlineStr"/>
@@ -4789,13 +4797,13 @@
         </is>
       </c>
       <c r="M70" s="2" t="n">
-        <v>2545.14</v>
+        <v>15194.46</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>1058078-3038-CM26</t>
+          <t>1057417-15577-CM26</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -4810,7 +4818,7 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -4820,17 +4828,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>61.602.123-0</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hospital de Melipilla</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4850,13 +4858,13 @@
         </is>
       </c>
       <c r="M71" s="2" t="n">
-        <v>8199.02</v>
+        <v>34172.86</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>1704-5313-CM26</t>
+          <t>1057417-15864-CM26</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -4871,7 +4879,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -4881,27 +4889,27 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.607.301-K</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>COMPLEJO ASISTENCIAL DR.VICTOR RIOS RUIZ</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K72" t="inlineStr"/>
@@ -4911,13 +4919,13 @@
         </is>
       </c>
       <c r="M72" s="2" t="n">
-        <v>9990.07</v>
+        <v>16875</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>1057539-7998-CM26</t>
+          <t>4817-3433-CM26</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -4932,57 +4940,53 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.625.950-7</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M73" s="2" t="n">
-        <v>7430.79</v>
+        <v>2545.14</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>1057491-5473-CM26</t>
+          <t>4502-683-CM26</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -4997,7 +5001,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -5007,43 +5011,47 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>61.608.408-9</t>
+          <t>61.606.917-9</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE LINARES</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>NEUMANN LIMITADA</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>78.936.310-2</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M74" s="2" t="n">
-        <v>5759.74</v>
+        <v>11549.37</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>1057539-7898-CM26</t>
+          <t>2111-12184-CM26</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5058,7 +5066,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -5068,17 +5076,17 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5098,13 +5106,13 @@
         </is>
       </c>
       <c r="M75" s="2" t="n">
-        <v>28598.42</v>
+        <v>3422.72</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>3191-5020-CM26</t>
+          <t>2111-12249-CM26</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5119,7 +5127,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -5129,43 +5137,47 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>61.102.017-1</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L76" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M76" s="2" t="n">
-        <v>7103.7</v>
+        <v>2472.17</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>1242131-981-CM26</t>
+          <t>2111-12341-CM26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5180,7 +5192,7 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -5190,27 +5202,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K77" t="inlineStr"/>
@@ -5220,13 +5232,13 @@
         </is>
       </c>
       <c r="M77" s="2" t="n">
-        <v>2586.25</v>
+        <v>3585.59</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>1057049-18545-CM26</t>
+          <t>2111-12471-CM26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5241,7 +5253,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -5251,12 +5263,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>61.608.604-9</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -5266,28 +5278,32 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>BIOIMPLANTES SA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>76.214.144-2</t>
-        </is>
-      </c>
-      <c r="K78" t="inlineStr"/>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L78" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M78" s="2" t="n">
-        <v>62230.66</v>
+        <v>3336.48</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>1057539-8024-CM26</t>
+          <t>2111-12494-CM26</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5302,37 +5318,37 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2026-09-27</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.602-2</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DE URGENCIA ASISTENCIA PUBLICA DR ALEJANDRO DEL RIO</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>TECNIKA S A</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>96.625.950-7</t>
         </is>
       </c>
       <c r="K79" t="inlineStr"/>
@@ -5342,13 +5358,13 @@
         </is>
       </c>
       <c r="M79" s="2" t="n">
-        <v>28095.39</v>
+        <v>2908.73</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>608-11651-CM26</t>
+          <t>1058078-3038-CM26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5363,37 +5379,37 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.602.123-0</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K80" t="inlineStr"/>
@@ -5403,13 +5419,13 @@
         </is>
       </c>
       <c r="M80" s="2" t="n">
-        <v>18524.55</v>
+        <v>8199.02</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>1057539-7411-CM26</t>
+          <t>1704-5313-CM26</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5424,27 +5440,27 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5464,13 +5480,13 @@
         </is>
       </c>
       <c r="M81" s="2" t="n">
-        <v>64519.04</v>
+        <v>9990.07</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>3328-2447-CM26</t>
+          <t>1057539-7998-CM26</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -5485,7 +5501,7 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -5495,43 +5511,47 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>61.103.007-K</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>TRIMED CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>76.556.146-9</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M82" s="2" t="n">
-        <v>5567.25</v>
+        <v>7430.79</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>1057539-8032-CM26</t>
+          <t>1057491-5473-CM26</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -5546,37 +5566,37 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.608.408-9</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD ORIENTE HOSPITAL LUIS CALVO MACKENNA</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>TARGET SITE CHILE SPA</t>
+          <t>NEUMANN LIMITADA</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>76.825.774-4</t>
+          <t>78.936.310-2</t>
         </is>
       </c>
       <c r="K83" t="inlineStr"/>
@@ -5586,13 +5606,13 @@
         </is>
       </c>
       <c r="M83" s="2" t="n">
-        <v>12096.26</v>
+        <v>5759.74</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>1057539-8040-CM26</t>
+          <t>3191-5020-CM26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -5607,27 +5627,27 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.102.017-1</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -5647,13 +5667,13 @@
         </is>
       </c>
       <c r="M84" s="2" t="n">
-        <v>12096.26</v>
+        <v>7103.7</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>608-11665-CM26</t>
+          <t>1057539-7898-CM26</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -5668,7 +5688,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -5678,27 +5698,27 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>61.606.602-1</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K85" t="inlineStr"/>
@@ -5708,13 +5728,13 @@
         </is>
       </c>
       <c r="M85" s="2" t="n">
-        <v>2870.44</v>
+        <v>28598.42</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>1057539-8097-CM26</t>
+          <t>1242131-981-CM26</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -5729,7 +5749,7 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -5739,47 +5759,43 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.404-5</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr"/>
       <c r="L86" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M86" s="2" t="n">
-        <v>2341.47</v>
+        <v>2586.25</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>1549-4205-CM26</t>
+          <t>1057049-18545-CM26</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -5794,22 +5810,22 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>61.608.002-4</t>
+          <t>61.608.604-9</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
+          <t>SERV SALUD METROPOLITANO CENTRAL HOSPITAL CLINICO SAN BORJA ARRIARAN</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -5819,12 +5835,12 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>BIOIMPLANTES SA</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>76.214.144-2</t>
         </is>
       </c>
       <c r="K87" t="inlineStr"/>
@@ -5834,13 +5850,13 @@
         </is>
       </c>
       <c r="M87" s="2" t="n">
-        <v>72274.78</v>
+        <v>62230.66</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>812030-974-CM26</t>
+          <t>1057539-8024-CM26</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -5855,7 +5871,7 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -5865,27 +5881,27 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
+          <t>SINERMED SPA</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>93.745.000-1</t>
+          <t>76.367.671-4</t>
         </is>
       </c>
       <c r="K88" t="inlineStr"/>
@@ -5895,13 +5911,13 @@
         </is>
       </c>
       <c r="M88" s="2" t="n">
-        <v>4383.67</v>
+        <v>28095.39</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>1057402-10002-CM26</t>
+          <t>1057539-7411-CM26</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -5916,57 +5932,53 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>TRIMED CHILE SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>76.556.146-9</t>
-        </is>
-      </c>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M89" s="2" t="n">
-        <v>4873.15</v>
+        <v>64519.04</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>1057402-10037-CM26</t>
+          <t>1057539-7513-CM26</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -5981,37 +5993,37 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>61.607.901-8</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Magallanes</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>TECNOMEDICAL S A</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
+          <t>99.585.860-6</t>
         </is>
       </c>
       <c r="K90" t="inlineStr"/>
@@ -6021,13 +6033,13 @@
         </is>
       </c>
       <c r="M90" s="2" t="n">
-        <v>4312.16</v>
+        <v>70972.92999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>1058078-3123-CM26</t>
+          <t>3328-2447-CM26</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -6042,22 +6054,22 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>61.602.123-0</t>
+          <t>61.103.007-K</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Hospital de Melipilla</t>
+          <t>FUERZA AEREA DE CHILE COMANDO LOGISTICO</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -6082,13 +6094,13 @@
         </is>
       </c>
       <c r="M91" s="2" t="n">
-        <v>4566.73</v>
+        <v>5567.25</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>699866-9383-CM26</t>
+          <t>1057539-8032-CM26</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -6103,57 +6115,53 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>61.606.901-2</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>DROGUERIA HOFMANN SAC</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>92.288.000-k</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M92" s="2" t="n">
-        <v>4638.75</v>
+        <v>12096.26</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2109-1998-CM26</t>
+          <t>1057539-8040-CM26</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -6168,7 +6176,7 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -6178,47 +6186,43 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>61.608.203-5</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>HARMONY MEDICAL SPA</t>
+          <t>TARGET SITE CHILE SPA</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
         <is>
-          <t>77.447.444-7</t>
-        </is>
-      </c>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.825.774-4</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M93" s="2" t="n">
-        <v>7246.98</v>
+        <v>12096.26</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2048-2857-CM26</t>
+          <t>608-11651-CM26</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -6233,7 +6237,7 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -6243,27 +6247,27 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>61.975.800-5</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>93.745.000-1</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -6277,13 +6281,13 @@
         </is>
       </c>
       <c r="M94" s="2" t="n">
-        <v>2256.49</v>
+        <v>18524.55</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>1057539-8154-CM26</t>
+          <t>608-11665-CM26</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -6298,7 +6302,7 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -6308,27 +6312,27 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>61.975.100-0</t>
+          <t>61.606.602-1</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+          <t>HOSPITAL DR GUSTAVO FRICKE DE VINA DEL MAR</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K95" t="inlineStr"/>
@@ -6338,13 +6342,13 @@
         </is>
       </c>
       <c r="M95" s="2" t="n">
-        <v>5518</v>
+        <v>2870.44</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>1704-5419-CM26</t>
+          <t>1058078-3123-CM26</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -6359,27 +6363,27 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>61.606.608-0</t>
+          <t>61.602.123-0</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
+          <t>Hospital de Melipilla</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6399,13 +6403,13 @@
         </is>
       </c>
       <c r="M96" s="2" t="n">
-        <v>12474.87</v>
+        <v>4566.73</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>1555-2843-CM26</t>
+          <t>1057539-8097-CM26</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -6420,53 +6424,57 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>61.606.303-0</t>
+          <t>61.975.100-0</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>BIOMET CHILE S A</t>
+          <t>DROGUERIA HOFMANN SAC</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>96.863.710-k</t>
-        </is>
-      </c>
-      <c r="K97" t="inlineStr"/>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L97" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M97" s="2" t="n">
-        <v>6312.14</v>
+        <v>2341.47</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2080-9967-CM26</t>
+          <t>1549-4205-CM26</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -6481,37 +6489,37 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>61.602.138-9</t>
+          <t>61.608.002-4</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+          <t>SERVICIO DE SALUD METROPOLITANA NORTE HOSPITAL SAN JOSE</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K98" t="inlineStr"/>
@@ -6521,13 +6529,13 @@
         </is>
       </c>
       <c r="M98" s="2" t="n">
-        <v>3521.22</v>
+        <v>72274.78</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>1242131-1226-CM26</t>
+          <t>1057402-10002-CM26</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -6542,37 +6550,37 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>61.606.404-5</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+          <t>TRIMED CHILE SPA</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>78.233.420-4</t>
+          <t>76.556.146-9</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -6586,13 +6594,13 @@
         </is>
       </c>
       <c r="M99" s="2" t="n">
-        <v>2305.97</v>
+        <v>4873.15</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>812030-953-CM26</t>
+          <t>699866-9383-CM26</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -6607,53 +6615,57 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.606.901-2</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE TALCA</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
+          <t>Maule</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>DROGUERIA HOFMANN SAC</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>92.288.000-k</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
-        </is>
-      </c>
-      <c r="J100" t="inlineStr">
-        <is>
-          <t>76.102.788-3</t>
-        </is>
-      </c>
-      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M100" s="2" t="n">
-        <v>40858.64</v>
+        <v>4638.75</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>812030-952-CM26</t>
+          <t>1057402-10037-CM26</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -6668,37 +6680,37 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>65.075.485-9</t>
+          <t>61.607.901-8</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+          <t>HOSPITAL CLINICO DE MAGALLANES DR. LAUTARO NAVARRO AVARIA</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+          <t>BIOMET CHILE S A</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
         <is>
-          <t>76.102.788-3</t>
+          <t>96.863.710-k</t>
         </is>
       </c>
       <c r="K101" t="inlineStr"/>
@@ -6708,13 +6720,13 @@
         </is>
       </c>
       <c r="M101" s="2" t="n">
-        <v>40018.36</v>
+        <v>4312.16</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>1213444-440-CM26</t>
+          <t>812030-974-CM26</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -6729,7 +6741,7 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -6739,43 +6751,47 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>71.328.600-1</t>
+          <t>65.075.485-9</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>HEMISFERIO SUR S.A.</t>
+          <t>JOHNSON Y JOHNSON DE CHILE S A</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>96.533.330-4</t>
-        </is>
-      </c>
-      <c r="K102" t="inlineStr"/>
+          <t>93.745.000-1</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L102" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M102" s="2" t="n">
-        <v>4463.45</v>
+        <v>4383.67</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2109-2016-CM26</t>
+          <t>1704-5419-CM26</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -6795,32 +6811,32 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>61.608.203-5</t>
+          <t>61.606.608-0</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+          <t>SERVICIO DE SALUD VINA DEL MAR QUILLOTA</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>SINERMED SPA</t>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
         <is>
-          <t>76.367.671-4</t>
+          <t>76.102.788-3</t>
         </is>
       </c>
       <c r="K103" t="inlineStr"/>
@@ -6830,6 +6846,750 @@
         </is>
       </c>
       <c r="M103" s="2" t="n">
+        <v>12474.87</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>1057539-8154-CM26</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="n">
+        <v>5518</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>2109-1998-CM26</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>61.608.203-5</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>HARMONY MEDICAL SPA</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>77.447.444-7</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="n">
+        <v>7246.98</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>2048-2857-CM26</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>61.975.800-5</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD CHILOE</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="n">
+        <v>2256.49</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>2080-10034-CM26</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>TECNOMEDICAL S A</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M107" s="2" t="n">
+        <v>44144.01</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>1555-2843-CM26</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>61.606.303-0</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>HOSPITAL PROVINCIAL   DEL HUASCO MSR FERNANDO ARIZTIA RUIZ</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Atacama</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>BIOMET CHILE S A</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>96.863.710-k</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M108" s="2" t="n">
+        <v>6312.14</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2080-9967-CM26</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>61.602.138-9</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD DEL LIBERTADOR B O'HIGGINS HOSPITAL REG RANCAGUA</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M109" s="2" t="n">
+        <v>3521.22</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>1242131-1226-CM26</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>61.606.404-5</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD COQUIMBO HOSPITAL DE O</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>HOSPITALIA PRODUCTOS MEDICOS LTDA</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>78.233.420-4</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M110" s="2" t="n">
+        <v>2305.97</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>812030-953-CM26</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M111" s="2" t="n">
+        <v>40858.64</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>812030-952-CM26</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>65.075.485-9</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>HOSPITAL CLINICO METROPOLITANO DE LA FLORIDA DOCTORA ELOISA DIAZ</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIALIZADORA DE INSUMOS MEDICOS CLP S.A.</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>76.102.788-3</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M112" s="2" t="n">
+        <v>40018.36</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>1057539-7515-CM26</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>61.975.100-0</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>HOSPITAL PUERTO MONTT SERVICIO DE SALUD DEL RELONCAVI</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>TECNOMEDICAL S A</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>99.585.860-6</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M113" s="2" t="n">
+        <v>15634.34</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>1213444-440-CM26</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>71.328.600-1</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>CORP MUNICIPAL SAN FERNANDO PARA LA ATENCION MENORES Y LAS A DE E Y S</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>O'Higgins</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>HEMISFERIO SUR S.A.</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>96.533.330-4</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M114" s="2" t="n">
+        <v>4463.45</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2109-2016-CM26</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>2239-15-LR25</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>61.608.203-5</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD OCCIDENTE INSTITUTO TRAUMATOLOGICO DE SANTIAGO</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>SINERMED SPA</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>76.367.671-4</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M115" s="2" t="n">
         <v>3004.25</v>
       </c>
     </row>
